--- a/docs/samples/supplier_offers.xlsx
+++ b/docs/samples/supplier_offers.xlsx
@@ -1491,12 +1491,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P-000007</t>
+          <t>P-000006</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1506,21 +1506,21 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A-07-00</t>
+          <t>B06X</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>67.69</v>
+        <v>65.73</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1542,11 +1542,11 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R8</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1567,21 +1567,21 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B07X</t>
+          <t>A-07-00</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>69.56</v>
+        <v>67.69</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1589,11 +1589,11 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1603,46 +1603,46 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R8</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R8</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P-000008</t>
+          <t>P-000007</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Freightliner Cascadia P3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A-08-00</t>
+          <t>B07X</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>71.86</v>
+        <v>69.56</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1650,11 +1650,11 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1664,11 +1664,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R9</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R8</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1689,25 +1689,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>B08X</t>
+          <t>A-08-00</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>73.39</v>
+        <v>71.86</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1725,11 +1725,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R9</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1750,58 +1750,58 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>供应商C</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C-2003</t>
+          <t>B08X</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>73.39</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R9</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v>2</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>供应商C目录.pdf!p1!t1!r5</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P-000009</t>
+          <t>P-000008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1811,25 +1811,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商C</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A-09-00</t>
+          <t>C-2003</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>76.03</v>
+        <v>70</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R10</t>
+          <t>供应商C目录.pdf!p1!t1!r5</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1872,33 +1872,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>B09X</t>
+          <t>A-09-00</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>77.22</v>
+        <v>76.03</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1908,11 +1908,11 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R10</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R10</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1933,21 +1933,21 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>供应商C</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C-2004</t>
+          <t>B09X</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>75</v>
+        <v>77.22</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1955,36 +1955,36 @@
         </is>
       </c>
       <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R10</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
         <v>2</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>供应商C目录.pdf!p2!t1!r1</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P-000010</t>
+          <t>P-000009</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商C</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A-10-00</t>
+          <t>C-2004</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>80.2</v>
+        <v>75</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2016,11 +2016,11 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2030,11 +2030,11 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R11</t>
+          <t>供应商C目录.pdf!p2!t1!r1</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2055,21 +2055,21 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>B10X</t>
+          <t>A-10-00</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>81.05</v>
+        <v>80.2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2077,11 +2077,11 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2091,22 +2091,22 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R11</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R11</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P-000011</t>
+          <t>P-000010</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Fan Shroud</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2116,21 +2116,21 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>A-11-00</t>
+          <t>B10X</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>84.37</v>
+        <v>81.05</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2152,22 +2152,22 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R12</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R11</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P-000011</t>
+          <t>P-000010</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Fan Shroud</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2177,21 +2177,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商C</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>B11X</t>
+          <t>C-2005</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>84.88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2199,11 +2199,11 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2213,11 +2213,11 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R12</t>
+          <t>供应商C目录.pdf!p1!t1!r6</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2238,21 +2238,21 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>供应商C</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C-2006</t>
+          <t>A-11-00</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>92.5</v>
+        <v>84.37</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2260,11 +2260,11 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2274,58 +2274,58 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r7</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R12</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P-000012</t>
+          <t>P-000011</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A-12-L</t>
+          <t>B11X</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>88.54000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2335,58 +2335,58 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R13</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R12</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P-000012</t>
+          <t>P-000011</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商C</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>B12L</t>
+          <t>C-2006</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>88.70999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,27 +2396,27 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
+          <t>供应商C目录.pdf!p1!t1!r7</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P-000013</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2431,23 +2431,23 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A-14-00</t>
+          <t>A-12-L</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>96.88</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R14</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R13</t>
         </is>
       </c>
       <c r="M33" t="n">
@@ -2467,40 +2467,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P-000014</t>
+          <t>P-000012</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A-16-00</t>
+          <t>B12L</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>105.22</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2518,22 +2518,22 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R15</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>P-000013</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2553,11 +2553,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>A-17-L</t>
+          <t>A-14-00</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>109.39</v>
+        <v>96.88</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2565,11 +2565,11 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R16</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R14</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2589,17 +2589,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P-000016</t>
+          <t>P-000014</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2614,11 +2614,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A-19-00</t>
+          <t>A-16-00</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>117.73</v>
+        <v>105.22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2626,11 +2626,11 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R17</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R15</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2650,17 +2650,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P-000017</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2675,15 +2675,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>A-21-00</t>
+          <t>A-17-L</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>126.07</v>
+        <v>109.39</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R18</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2711,17 +2711,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P-000018</t>
+          <t>P-000016</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Freightliner Cascadia P3</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2736,11 +2736,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>A-22-00</t>
+          <t>A-19-00</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>130.24</v>
+        <v>117.73</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R19</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R17</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2772,12 +2772,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>P-000019</t>
+          <t>P-000017</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Fan Shroud</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2797,11 +2797,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>A-24-00</t>
+          <t>A-21-00</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>138.58</v>
+        <v>126.07</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2809,11 +2809,11 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R20</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R18</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2833,17 +2833,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>P-000020</t>
+          <t>P-000018</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Freightliner Cascadia P3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2858,11 +2858,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>A-25-L</t>
+          <t>A-22-00</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>142.75</v>
+        <v>130.24</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2870,11 +2870,11 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R21</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R19</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2894,7 +2894,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>P-000021</t>
+          <t>P-000019</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2919,11 +2919,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A-27-00</t>
+          <t>A-24-00</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>151.09</v>
+        <v>138.58</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2931,11 +2931,11 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R22</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R20</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2955,17 +2955,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P-000022</t>
+          <t>P-000020</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2980,11 +2980,11 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>A-29-00</t>
+          <t>A-25-L</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>159.43</v>
+        <v>142.75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R23</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R21</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -3016,12 +3016,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>P-000021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3041,15 +3041,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>A-31-L</t>
+          <t>A-27-00</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>167.77</v>
+        <v>151.09</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R24</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R22</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -3077,12 +3077,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>P-000022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3102,17 +3102,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A-33-00</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>（缺失）</t>
-        </is>
+          <t>A-29-00</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>159.43</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>（缺失）</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3120,7 +3118,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3130,7 +3128,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R23</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -3140,15 +3138,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P-000025</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Side Grille</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Volvo VNL 2018-2023</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>A</t>
@@ -3161,11 +3163,11 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>A-35-00</t>
+          <t>A-31-L</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>184.45</v>
+        <v>167.77</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3177,7 +3179,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3187,7 +3189,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -3197,7 +3199,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>P-000026</t>
+          <t>P-000024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3207,7 +3209,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Freightliner Cascadia P3</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3222,23 +3224,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A-38-00</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>196.96</v>
+          <t>A-33-00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>（缺失）</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>（缺失）</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3248,7 +3252,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R27</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3258,19 +3262,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>P-000025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Side Grille</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Volvo VNL 2018-2023</t>
-        </is>
-      </c>
+          <t>Fan Shroud</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>A</t>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>A-40-L</t>
+          <t>A-35-00</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>205.3</v>
+        <v>184.45</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3295,11 +3295,11 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -3319,36 +3319,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>P-000026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Volvo VN</t>
+          <t>Freightliner Cascadia P3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>B13R</t>
+          <t>A-38-00</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>92.54000000000001</v>
+        <v>196.96</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R27</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P-000041</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3395,21 +3395,21 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>B15X</t>
+          <t>A-40-L</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>100.2</v>
+        <v>205.3</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3417,11 +3417,11 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Volvo VN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3466,11 +3466,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>B18R</t>
+          <t>B13R</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>111.69</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3478,11 +3478,11 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -3502,17 +3502,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>P-000043</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3527,23 +3527,23 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>B20X</t>
+          <t>B15X</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>119.35</v>
+        <v>100.2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3563,17 +3563,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>P-000044</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Freightliner Cascadia P3</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>B23X</t>
+          <t>B18R</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>130.84</v>
+        <v>111.69</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3600,11 +3600,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3624,17 +3624,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P-000045</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3649,23 +3649,23 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>B26R</t>
+          <t>B20X</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>142.33</v>
+        <v>119.35</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3685,7 +3685,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P-000046</t>
+          <t>P-000044</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Cascadia P3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3710,23 +3710,23 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B28X</t>
+          <t>B23X</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>149.99</v>
+        <v>130.84</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3746,17 +3746,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>P-000045</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3771,11 +3771,11 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>B30X</t>
+          <t>B26R</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>157.65</v>
+        <v>142.33</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3807,12 +3807,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>P-000046</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3832,11 +3832,11 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B32R</t>
+          <t>B28X</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>165.31</v>
+        <v>149.99</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -3868,12 +3868,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>P-000049</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3893,17 +3893,15 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B34X</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>（缺失）</t>
-        </is>
+          <t>B30X</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>157.65</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>（缺失）</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3911,7 +3909,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3921,7 +3919,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -3931,7 +3929,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>P-000050</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3939,7 +3937,11 @@
           <t>Side Grille</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Volvo VNL 2018-2023</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>B</t>
@@ -3952,11 +3954,11 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36L</t>
+          <t>B32R</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>180.63</v>
+        <v>165.31</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3968,7 +3970,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3978,7 +3980,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -3988,12 +3990,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>P-000049</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4013,25 +4015,25 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B37X</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>184.46</v>
+          <t>B34X</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>（缺失）</t>
+        </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
           <t>（缺失）</t>
         </is>
       </c>
+      <c r="I59" t="n">
+        <v>10</v>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4041,7 +4043,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -4051,19 +4053,15 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P-000052</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Freightliner Cascadia P3</t>
-        </is>
-      </c>
+          <t>Side Grille</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>B</t>
@@ -4076,23 +4074,23 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B39X</t>
+          <t>B36L</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>192.12</v>
+        <v>180.63</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4102,7 +4100,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -4112,17 +4110,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4137,23 +4135,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>B41R</t>
+          <t>B37X</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>199.78</v>
+        <v>184.46</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>5</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>（缺失）</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -4173,36 +4173,36 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P-000054</t>
+          <t>P-000052</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Cascadia P3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>A-42-00</t>
+          <t>B39X</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61.2</v>
+        <v>192.12</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4210,11 +4210,11 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4224,17 +4224,17 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R28</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>P-000055</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4244,26 +4244,26 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>A-43-R</t>
+          <t>B41R</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>139</v>
+        <v>199.78</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4271,34 +4271,38 @@
         </is>
       </c>
       <c r="I63" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
         <v>2</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>P-000056</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>P-000054</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Fan Shroud</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>Volvo VNL 2018-2023</t>
@@ -4316,11 +4320,11 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>A-44-00</t>
+          <t>A-42-00</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>12.5</v>
+        <v>61.2</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4328,7 +4332,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R30</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -4352,36 +4356,36 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>P-000057</t>
+          <t>P-000055</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Freightliner Cascadia P3</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>B06X</t>
+          <t>A-43-R</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>65.73</v>
+        <v>139</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4389,11 +4393,11 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4403,24 +4407,20 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>P-000060</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Side Grille</t>
-        </is>
-      </c>
+          <t>P-000056</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>Volvo VNL 2018-2023</t>
@@ -4428,21 +4428,21 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>供应商C</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C-1003-R</t>
+          <t>A-44-00</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4450,11 +4450,11 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4464,27 +4464,27 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r4</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R30</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>P-000062</t>
+          <t>P-000059</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4499,11 +4499,11 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C-2005</t>
+          <t>C-1003-R</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>供应商C目录.pdf!p1!t1!r6</t>
+          <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -4535,7 +4535,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>P-000065</t>
+          <t>P-000064</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>

--- a/docs/samples/supplier_offers.xlsx
+++ b/docs/samples/supplier_offers.xlsx
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Volvo VN 2006-2017</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2467,73 +2467,73 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P-000012</t>
+          <t>P-000013</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>B12L</t>
+          <t>A-14-00</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>88.70999999999999</v>
+        <v>96.88</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R14</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P-000013</t>
+          <t>P-000014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2553,11 +2553,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>A-14-00</t>
+          <t>A-16-00</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>96.88</v>
+        <v>105.22</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2565,11 +2565,11 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R14</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R15</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2589,12 +2589,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P-000014</t>
+          <t>P-000015</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2614,11 +2614,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A-16-00</t>
+          <t>A-17-L</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>105.22</v>
+        <v>109.39</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2626,11 +2626,11 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R15</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R16</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2650,17 +2650,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P-000015</t>
+          <t>P-000016</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2675,11 +2675,11 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>A-17-L</t>
+          <t>A-19-00</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>109.39</v>
+        <v>117.73</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R16</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R17</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2711,12 +2711,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P-000016</t>
+          <t>P-000017</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Fan Shroud</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2736,23 +2736,23 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>A-19-00</t>
+          <t>A-21-00</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>117.73</v>
+        <v>126.07</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R17</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R18</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2772,17 +2772,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>P-000017</t>
+          <t>P-000018</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Freightliner Cascadia P3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2797,23 +2797,23 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>A-21-00</t>
+          <t>A-22-00</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>126.07</v>
+        <v>130.24</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R18</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R19</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2833,7 +2833,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>P-000018</t>
+          <t>P-000019</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Freightliner Cascadia P3</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2858,23 +2858,23 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>A-22-00</t>
+          <t>A-24-00</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>130.24</v>
+        <v>138.58</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R19</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R20</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2894,17 +2894,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>P-000019</t>
+          <t>P-000020</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2919,23 +2919,23 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A-24-00</t>
+          <t>A-25-L</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>138.58</v>
+        <v>142.75</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R20</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R21</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2955,17 +2955,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P-000020</t>
+          <t>P-000021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2980,23 +2980,23 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>A-25-L</t>
+          <t>A-27-00</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>142.75</v>
+        <v>151.09</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R21</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R22</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -3016,17 +3016,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P-000021</t>
+          <t>P-000022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Air Filter Housing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3041,23 +3041,23 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>A-27-00</t>
+          <t>A-29-00</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>151.09</v>
+        <v>159.43</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R22</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R23</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -3077,17 +3077,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P-000022</t>
+          <t>P-000023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Air Filter Housing</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3102,11 +3102,11 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A-29-00</t>
+          <t>A-31-L</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>159.43</v>
+        <v>167.77</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3114,11 +3114,11 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R23</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R24</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P-000023</t>
+          <t>P-000024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3163,23 +3163,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>A-31-L</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>167.77</v>
+          <t>A-33-00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>（缺失）</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>（缺失）</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3189,7 +3191,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R24</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -3199,19 +3201,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>P-000024</t>
+          <t>P-000025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Front Grille</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Freightliner Century</t>
-        </is>
-      </c>
+          <t>Fan Shroud</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>A</t>
@@ -3224,25 +3222,23 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A-33-00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>（缺失）</t>
-        </is>
+          <t>A-35-00</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>184.45</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>（缺失）</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3252,7 +3248,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R25</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3262,15 +3258,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P-000025</t>
+          <t>P-000026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Front Grille</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Freightliner Cascadia P3</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>A</t>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>A-35-00</t>
+          <t>A-38-00</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>184.45</v>
+        <v>196.96</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3295,11 +3295,11 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R26</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R27</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -3319,17 +3319,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>P-000026</t>
+          <t>P-000027</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Freightliner Cascadia P3</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3344,11 +3344,11 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>A-38-00</t>
+          <t>A-40-L</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>196.96</v>
+        <v>205.3</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3356,11 +3356,11 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R27</t>
+          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -3380,7 +3380,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P-000027</t>
+          <t>P-000040</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3390,26 +3390,26 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Volvo VN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>A-40-L</t>
+          <t>B13R</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>205.3</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3417,11 +3417,11 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3431,27 +3431,27 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P-000040</t>
+          <t>P-000041</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Front Grille</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Volvo VN</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3466,11 +3466,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>B13R</t>
+          <t>B15X</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>92.54000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3478,11 +3478,11 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -3502,12 +3502,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>P-000041</t>
+          <t>P-000042</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Front Grille</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3527,11 +3527,11 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>B15X</t>
+          <t>B18R</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>100.2</v>
+        <v>111.69</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3539,11 +3539,11 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3563,17 +3563,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>P-000042</t>
+          <t>P-000043</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3588,23 +3588,23 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>B18R</t>
+          <t>B20X</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>111.69</v>
+        <v>119.35</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3624,17 +3624,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P-000043</t>
+          <t>P-000044</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Freightliner Cascadia P3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3649,23 +3649,23 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>B20X</t>
+          <t>B23X</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>119.35</v>
+        <v>130.84</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3685,17 +3685,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P-000044</t>
+          <t>P-000045</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Freightliner Cascadia P3</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3710,11 +3710,11 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B23X</t>
+          <t>B26R</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>130.84</v>
+        <v>142.33</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3722,11 +3722,11 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3746,17 +3746,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>P-000045</t>
+          <t>P-000046</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3771,23 +3771,23 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>B26R</t>
+          <t>B28X</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>142.33</v>
+        <v>149.99</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3807,17 +3807,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>P-000046</t>
+          <t>P-000047</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Air Filter Housing Cap</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3832,23 +3832,23 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B28X</t>
+          <t>B30X</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>149.99</v>
+        <v>157.65</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -3868,17 +3868,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>P-000047</t>
+          <t>P-000048</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3893,23 +3893,23 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B30X</t>
+          <t>B32R</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>157.65</v>
+        <v>165.31</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -3929,17 +3929,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>P-000048</t>
+          <t>P-000049</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Freightliner Century</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3954,23 +3954,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B32R</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>165.31</v>
+          <t>B34X</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>（缺失）</t>
+        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>（缺失）</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3980,7 +3982,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -3990,19 +3992,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P-000049</t>
+          <t>P-000050</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Freightliner Century</t>
-        </is>
-      </c>
+          <t>Side Grille</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>B</t>
@@ -4015,25 +4013,23 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B34X</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>（缺失）</t>
-        </is>
+          <t>B36L</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>180.63</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>（缺失）</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4043,7 +4039,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -4053,15 +4049,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P-000050</t>
+          <t>P-000051</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Side Grille</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Air Filter Housing Cap</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Freightliner Century</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>B</t>
@@ -4074,23 +4074,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B36L</t>
+          <t>B37X</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>180.63</v>
+        <v>184.46</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1</v>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>（缺失）</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4100,7 +4102,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -4110,17 +4112,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>P-000051</t>
+          <t>P-000052</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Air Filter Housing Cap</t>
+          <t>Bug Screen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Freightliner Century</t>
+          <t>Freightliner Cascadia P3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4135,25 +4137,23 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>B37X</t>
+          <t>B39X</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>184.46</v>
+        <v>192.12</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>（缺失）</t>
-        </is>
+      <c r="I61" t="n">
+        <v>20</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -4173,17 +4173,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P-000052</t>
+          <t>P-000053</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bug Screen</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Freightliner Cascadia P3</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4198,11 +4198,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>B39X</t>
+          <t>B41R</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>192.12</v>
+        <v>199.78</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4210,11 +4210,11 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -4234,12 +4234,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>P-000053</t>
+          <t>P-000054</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Side Grille</t>
+          <t>Fan Shroud</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4249,21 +4249,21 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>供应商B</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>B41R</t>
+          <t>A-42-00</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>199.78</v>
+        <v>61.2</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4285,27 +4285,27 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R28</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>P-000054</t>
+          <t>P-000055</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fan Shroud</t>
+          <t>Side Grille</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4320,11 +4320,11 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>A-42-00</t>
+          <t>A-43-R</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61.2</v>
+        <v>139</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R28</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -4356,17 +4356,13 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>P-000055</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Side Grille</t>
-        </is>
-      </c>
+          <t>P-000056</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Volvo VNL 2018-2023</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4381,11 +4377,11 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>A-43-R</t>
+          <t>A-44-00</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>139</v>
+        <v>12.5</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4393,7 +4389,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4407,7 +4403,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
+          <t>供应商A报价表_v2.xlsx!报价明细!R30</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -4417,44 +4413,48 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>P-000056</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>P-000057</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Side Grille</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Volvo VNL 2018-2023</t>
+          <t>Volvo VN 2004-2017</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>供应商A</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>A-44-00</t>
+          <t>B12L</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>12.5</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4464,17 +4464,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>供应商A报价表_v2.xlsx!报价明细!R30</t>
+          <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>P-000059</t>
+          <t>P-000060</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4535,7 +4535,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>P-000064</t>
+          <t>P-000065</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>

--- a/docs/samples/supplier_offers.xlsx
+++ b/docs/samples/supplier_offers.xlsx
@@ -4603,6 +4603,9 @@
   </sheetPr>
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
